--- a/backtest_report.xlsx
+++ b/backtest_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G121"/>
+  <dimension ref="A1:G196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
@@ -477,16 +477,16 @@
         <v>501</v>
       </c>
       <c r="D2" t="n">
-        <v>173.09</v>
+        <v>347.58</v>
       </c>
       <c r="E2" t="n">
-        <v>14.1877</v>
+        <v>21.939</v>
       </c>
       <c r="F2" t="n">
-        <v>18.038</v>
+        <v>43.6317</v>
       </c>
       <c r="G2" t="n">
-        <v>6.79</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="3">
@@ -501,19 +501,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="D3" t="n">
-        <v>173.09</v>
+        <v>347.58</v>
       </c>
       <c r="E3" t="n">
-        <v>23.6654</v>
+        <v>39.3989</v>
       </c>
       <c r="F3" t="n">
-        <v>29.8318</v>
+        <v>57.7289</v>
       </c>
       <c r="G3" t="n">
-        <v>10.27</v>
+        <v>14.72</v>
       </c>
     </row>
     <row r="4">
@@ -528,25 +528,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="D4" t="n">
-        <v>173.09</v>
+        <v>347.58</v>
       </c>
       <c r="E4" t="n">
-        <v>18.2092</v>
+        <v>29.5316</v>
       </c>
       <c r="F4" t="n">
-        <v>25.3217</v>
+        <v>49.3194</v>
       </c>
       <c r="G4" t="n">
-        <v>8.07</v>
+        <v>11.18</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>American: Airbnb (ABNB)</t>
+          <t>American: ASML (ASML)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -558,22 +558,22 @@
         <v>501</v>
       </c>
       <c r="D5" t="n">
-        <v>16.86</v>
+        <v>126.61</v>
       </c>
       <c r="E5" t="n">
-        <v>2.1235</v>
+        <v>260.9474</v>
       </c>
       <c r="F5" t="n">
-        <v>2.8379</v>
+        <v>284.4395</v>
       </c>
       <c r="G5" t="n">
-        <v>1.67</v>
+        <v>18.62</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>American: Airbnb (ABNB)</t>
+          <t>American: ASML (ASML)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -582,25 +582,25 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="D6" t="n">
-        <v>16.86</v>
+        <v>126.61</v>
       </c>
       <c r="E6" t="n">
-        <v>2.0173</v>
+        <v>257.4278</v>
       </c>
       <c r="F6" t="n">
-        <v>2.7077</v>
+        <v>320.8148</v>
       </c>
       <c r="G6" t="n">
-        <v>1.61</v>
+        <v>18.79</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>American: Airbnb (ABNB)</t>
+          <t>American: ASML (ASML)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -609,25 +609,25 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="D7" t="n">
-        <v>16.86</v>
+        <v>126.61</v>
       </c>
       <c r="E7" t="n">
-        <v>2.0437</v>
+        <v>189.548</v>
       </c>
       <c r="F7" t="n">
-        <v>2.8142</v>
+        <v>266.818</v>
       </c>
       <c r="G7" t="n">
-        <v>1.61</v>
+        <v>14.06</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>American: Amazon (AMZN)</t>
+          <t>American: Accenture (ACN)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -639,22 +639,22 @@
         <v>501</v>
       </c>
       <c r="D8" t="n">
-        <v>34.7</v>
+        <v>-40.8</v>
       </c>
       <c r="E8" t="n">
-        <v>4.6951</v>
+        <v>28.7084</v>
       </c>
       <c r="F8" t="n">
-        <v>6.1446</v>
+        <v>35.5357</v>
       </c>
       <c r="G8" t="n">
-        <v>2.1</v>
+        <v>14.67</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>American: Amazon (AMZN)</t>
+          <t>American: Accenture (ACN)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -663,25 +663,25 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="D9" t="n">
-        <v>34.7</v>
+        <v>-40.8</v>
       </c>
       <c r="E9" t="n">
-        <v>4.9894</v>
+        <v>21.2084</v>
       </c>
       <c r="F9" t="n">
-        <v>6.714</v>
+        <v>28.6077</v>
       </c>
       <c r="G9" t="n">
-        <v>2.17</v>
+        <v>10.48</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>American: Amazon (AMZN)</t>
+          <t>American: Accenture (ACN)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -690,25 +690,25 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="D10" t="n">
-        <v>34.7</v>
+        <v>-40.8</v>
       </c>
       <c r="E10" t="n">
-        <v>4.6794</v>
+        <v>19.3636</v>
       </c>
       <c r="F10" t="n">
-        <v>6.3052</v>
+        <v>29.856</v>
       </c>
       <c r="G10" t="n">
-        <v>2.04</v>
+        <v>9.640000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>American: Apple (AAPL)</t>
+          <t>American: Adobe (ADBE)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -720,22 +720,22 @@
         <v>501</v>
       </c>
       <c r="D11" t="n">
-        <v>31.19</v>
+        <v>-34.1</v>
       </c>
       <c r="E11" t="n">
-        <v>5.6287</v>
+        <v>53.5275</v>
       </c>
       <c r="F11" t="n">
-        <v>6.6929</v>
+        <v>61.7586</v>
       </c>
       <c r="G11" t="n">
-        <v>2.12</v>
+        <v>21.08</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>American: Apple (AAPL)</t>
+          <t>American: Adobe (ADBE)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -744,25 +744,25 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="D12" t="n">
-        <v>31.19</v>
+        <v>-34.1</v>
       </c>
       <c r="E12" t="n">
-        <v>13.5323</v>
+        <v>51.1474</v>
       </c>
       <c r="F12" t="n">
-        <v>16.2817</v>
+        <v>65.31440000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>5.04</v>
+        <v>19.64</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>American: Apple (AAPL)</t>
+          <t>American: Adobe (ADBE)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -771,25 +771,25 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="D13" t="n">
-        <v>31.19</v>
+        <v>-34.1</v>
       </c>
       <c r="E13" t="n">
-        <v>11.5741</v>
+        <v>16.2761</v>
       </c>
       <c r="F13" t="n">
-        <v>15.1672</v>
+        <v>23.0408</v>
       </c>
       <c r="G13" t="n">
-        <v>4.37</v>
+        <v>6.09</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>American: Costco (COST)</t>
+          <t>American: Airbnb (ABNB)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -801,22 +801,22 @@
         <v>501</v>
       </c>
       <c r="D14" t="n">
-        <v>1.74</v>
+        <v>11.95</v>
       </c>
       <c r="E14" t="n">
-        <v>11.4873</v>
+        <v>2.2301</v>
       </c>
       <c r="F14" t="n">
-        <v>13.812</v>
+        <v>2.936</v>
       </c>
       <c r="G14" t="n">
-        <v>1.22</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>American: Costco (COST)</t>
+          <t>American: Airbnb (ABNB)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -825,25 +825,25 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="D15" t="n">
-        <v>1.74</v>
+        <v>11.95</v>
       </c>
       <c r="E15" t="n">
-        <v>10.8486</v>
+        <v>1.9381</v>
       </c>
       <c r="F15" t="n">
-        <v>13.4747</v>
+        <v>2.6386</v>
       </c>
       <c r="G15" t="n">
-        <v>1.16</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>American: Costco (COST)</t>
+          <t>American: Airbnb (ABNB)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -852,25 +852,25 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="D16" t="n">
-        <v>1.74</v>
+        <v>11.95</v>
       </c>
       <c r="E16" t="n">
-        <v>10.2244</v>
+        <v>2.0453</v>
       </c>
       <c r="F16" t="n">
-        <v>12.8023</v>
+        <v>2.7967</v>
       </c>
       <c r="G16" t="n">
-        <v>1.09</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>American: Invesco QQQ (QQQ)</t>
+          <t>American: Alphabet/Google (GOOGL)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -882,22 +882,22 @@
         <v>501</v>
       </c>
       <c r="D17" t="n">
-        <v>39.01</v>
+        <v>160.69</v>
       </c>
       <c r="E17" t="n">
-        <v>8.5526</v>
+        <v>16.9528</v>
       </c>
       <c r="F17" t="n">
-        <v>11.0854</v>
+        <v>24.7789</v>
       </c>
       <c r="G17" t="n">
-        <v>1.41</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>American: Invesco QQQ (QQQ)</t>
+          <t>American: Alphabet/Google (GOOGL)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -906,25 +906,25 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="D18" t="n">
-        <v>39.01</v>
+        <v>160.69</v>
       </c>
       <c r="E18" t="n">
-        <v>38.2644</v>
+        <v>61.8465</v>
       </c>
       <c r="F18" t="n">
-        <v>40.8555</v>
+        <v>69.18980000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>6.25</v>
+        <v>19.21</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>American: Invesco QQQ (QQQ)</t>
+          <t>American: Alphabet/Google (GOOGL)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -933,25 +933,25 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="D19" t="n">
-        <v>39.01</v>
+        <v>160.69</v>
       </c>
       <c r="E19" t="n">
-        <v>68.3044</v>
+        <v>91.9385</v>
       </c>
       <c r="F19" t="n">
-        <v>72.3437</v>
+        <v>103.8996</v>
       </c>
       <c r="G19" t="n">
-        <v>11.32</v>
+        <v>29.9</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>American: Meta (META)</t>
+          <t>American: Amazon (AMZN)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -963,22 +963,22 @@
         <v>501</v>
       </c>
       <c r="D20" t="n">
-        <v>22.26</v>
+        <v>41.96</v>
       </c>
       <c r="E20" t="n">
-        <v>10.3893</v>
+        <v>7.6603</v>
       </c>
       <c r="F20" t="n">
-        <v>14.8284</v>
+        <v>11.722</v>
       </c>
       <c r="G20" t="n">
-        <v>1.63</v>
+        <v>3.15</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>American: Meta (META)</t>
+          <t>American: Amazon (AMZN)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -987,25 +987,25 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="D21" t="n">
-        <v>22.26</v>
+        <v>41.96</v>
       </c>
       <c r="E21" t="n">
-        <v>11.8067</v>
+        <v>7.9855</v>
       </c>
       <c r="F21" t="n">
-        <v>17.6908</v>
+        <v>12.0904</v>
       </c>
       <c r="G21" t="n">
-        <v>1.81</v>
+        <v>3.29</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>American: Meta (META)</t>
+          <t>American: Amazon (AMZN)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1014,25 +1014,25 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="D22" t="n">
-        <v>22.26</v>
+        <v>41.96</v>
       </c>
       <c r="E22" t="n">
-        <v>23.1368</v>
+        <v>7.045</v>
       </c>
       <c r="F22" t="n">
-        <v>32.3036</v>
+        <v>10.9619</v>
       </c>
       <c r="G22" t="n">
-        <v>3.24</v>
+        <v>2.93</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>American: Microsoft (MSFT)</t>
+          <t>American: Apple (AAPL)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1044,22 +1044,22 @@
         <v>501</v>
       </c>
       <c r="D23" t="n">
+        <v>49.17</v>
+      </c>
+      <c r="E23" t="n">
+        <v>5.162</v>
+      </c>
+      <c r="F23" t="n">
+        <v>6.4756</v>
+      </c>
+      <c r="G23" t="n">
         <v>1.97</v>
-      </c>
-      <c r="E23" t="n">
-        <v>10.165</v>
-      </c>
-      <c r="F23" t="n">
-        <v>13.1964</v>
-      </c>
-      <c r="G23" t="n">
-        <v>2.34</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>American: Microsoft (MSFT)</t>
+          <t>American: Apple (AAPL)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1068,25 +1068,25 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="D24" t="n">
-        <v>1.97</v>
+        <v>49.17</v>
       </c>
       <c r="E24" t="n">
-        <v>8.4297</v>
+        <v>13.7388</v>
       </c>
       <c r="F24" t="n">
-        <v>11.738</v>
+        <v>16.5113</v>
       </c>
       <c r="G24" t="n">
-        <v>1.86</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>American: Microsoft (MSFT)</t>
+          <t>American: Apple (AAPL)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1095,25 +1095,25 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="D25" t="n">
-        <v>1.97</v>
+        <v>49.17</v>
       </c>
       <c r="E25" t="n">
-        <v>15.164</v>
+        <v>13.657</v>
       </c>
       <c r="F25" t="n">
-        <v>19.1215</v>
+        <v>17.1206</v>
       </c>
       <c r="G25" t="n">
-        <v>3.09</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>American: Netflix (NFLX)</t>
+          <t>American: Broadcom (AVGO)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1125,22 +1125,22 @@
         <v>501</v>
       </c>
       <c r="D26" t="n">
-        <v>15.74</v>
+        <v>108.64</v>
       </c>
       <c r="E26" t="n">
-        <v>2.3937</v>
+        <v>14.4636</v>
       </c>
       <c r="F26" t="n">
-        <v>3.0817</v>
+        <v>19.8412</v>
       </c>
       <c r="G26" t="n">
-        <v>2.66</v>
+        <v>4.02</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>American: Netflix (NFLX)</t>
+          <t>American: Broadcom (AVGO)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1149,25 +1149,25 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="D27" t="n">
-        <v>15.74</v>
+        <v>108.64</v>
       </c>
       <c r="E27" t="n">
-        <v>2.4749</v>
+        <v>21.8065</v>
       </c>
       <c r="F27" t="n">
-        <v>3.2844</v>
+        <v>31.6634</v>
       </c>
       <c r="G27" t="n">
-        <v>2.53</v>
+        <v>5.78</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>American: Netflix (NFLX)</t>
+          <t>American: Broadcom (AVGO)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1176,25 +1176,25 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="D28" t="n">
-        <v>15.74</v>
+        <v>108.64</v>
       </c>
       <c r="E28" t="n">
-        <v>2.46</v>
+        <v>64.8068</v>
       </c>
       <c r="F28" t="n">
-        <v>3.3541</v>
+        <v>73.2645</v>
       </c>
       <c r="G28" t="n">
-        <v>2.38</v>
+        <v>18.15</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>American: PepsiCo (PEP)</t>
+          <t>American: Cisco (CSCO)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1206,22 +1206,22 @@
         <v>501</v>
       </c>
       <c r="D29" t="n">
-        <v>12.14</v>
+        <v>65.45</v>
       </c>
       <c r="E29" t="n">
-        <v>1.9792</v>
+        <v>3.9549</v>
       </c>
       <c r="F29" t="n">
-        <v>2.809</v>
+        <v>6.0297</v>
       </c>
       <c r="G29" t="n">
-        <v>1.29</v>
+        <v>4.62</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>American: PepsiCo (PEP)</t>
+          <t>American: Cisco (CSCO)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1230,25 +1230,25 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="D30" t="n">
-        <v>12.14</v>
+        <v>65.45</v>
       </c>
       <c r="E30" t="n">
-        <v>1.8158</v>
+        <v>10.7237</v>
       </c>
       <c r="F30" t="n">
-        <v>2.5099</v>
+        <v>12.2319</v>
       </c>
       <c r="G30" t="n">
-        <v>1.21</v>
+        <v>13.31</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>American: PepsiCo (PEP)</t>
+          <t>American: Cisco (CSCO)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1257,25 +1257,25 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="D31" t="n">
-        <v>12.14</v>
+        <v>65.45</v>
       </c>
       <c r="E31" t="n">
-        <v>2.2045</v>
+        <v>8.242100000000001</v>
       </c>
       <c r="F31" t="n">
-        <v>3.0718</v>
+        <v>10.6581</v>
       </c>
       <c r="G31" t="n">
-        <v>1.52</v>
+        <v>10.27</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>American: Tesla (TSLA)</t>
+          <t>American: Costco (COST)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1287,22 +1287,22 @@
         <v>501</v>
       </c>
       <c r="D32" t="n">
-        <v>44.35</v>
+        <v>0.67</v>
       </c>
       <c r="E32" t="n">
-        <v>12.4641</v>
+        <v>10.8094</v>
       </c>
       <c r="F32" t="n">
-        <v>17.6339</v>
+        <v>13.0845</v>
       </c>
       <c r="G32" t="n">
-        <v>2.86</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>American: Tesla (TSLA)</t>
+          <t>American: Costco (COST)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1311,25 +1311,25 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="D33" t="n">
-        <v>44.35</v>
+        <v>0.67</v>
       </c>
       <c r="E33" t="n">
-        <v>17.9379</v>
+        <v>10.5898</v>
       </c>
       <c r="F33" t="n">
-        <v>23.1908</v>
+        <v>13.1583</v>
       </c>
       <c r="G33" t="n">
-        <v>4.09</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>American: Tesla (TSLA)</t>
+          <t>American: Costco (COST)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1338,25 +1338,25 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="D34" t="n">
-        <v>44.35</v>
+        <v>0.67</v>
       </c>
       <c r="E34" t="n">
-        <v>15.2987</v>
+        <v>10.1673</v>
       </c>
       <c r="F34" t="n">
-        <v>20.5263</v>
+        <v>12.9264</v>
       </c>
       <c r="G34" t="n">
-        <v>3.67</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>American: Walmart (WMT)</t>
+          <t>American: Intel (INTC)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1368,22 +1368,22 @@
         <v>501</v>
       </c>
       <c r="D35" t="n">
-        <v>35.95</v>
+        <v>494.86</v>
       </c>
       <c r="E35" t="n">
-        <v>14.6366</v>
+        <v>13.9837</v>
       </c>
       <c r="F35" t="n">
-        <v>16.0783</v>
+        <v>22.7198</v>
       </c>
       <c r="G35" t="n">
-        <v>11.95</v>
+        <v>20.54</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>American: Walmart (WMT)</t>
+          <t>American: Intel (INTC)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1392,25 +1392,25 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="D36" t="n">
-        <v>35.95</v>
+        <v>494.86</v>
       </c>
       <c r="E36" t="n">
-        <v>14.4784</v>
+        <v>6.7014</v>
       </c>
       <c r="F36" t="n">
-        <v>17.4876</v>
+        <v>15.6662</v>
       </c>
       <c r="G36" t="n">
-        <v>12.06</v>
+        <v>9.25</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>American: Walmart (WMT)</t>
+          <t>American: Intel (INTC)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1419,25 +1419,25 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="D37" t="n">
-        <v>35.95</v>
+        <v>494.86</v>
       </c>
       <c r="E37" t="n">
-        <v>11.9345</v>
+        <v>5.2456</v>
       </c>
       <c r="F37" t="n">
-        <v>16.2163</v>
+        <v>13.6105</v>
       </c>
       <c r="G37" t="n">
-        <v>10</v>
+        <v>7.74</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Commodity: Coffee</t>
+          <t>American: Invesco QQQ (QQQ)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1446,25 +1446,25 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="D38" t="n">
-        <v>-17.06</v>
+        <v>46.36</v>
       </c>
       <c r="E38" t="n">
-        <v>6.6184</v>
+        <v>13.4106</v>
       </c>
       <c r="F38" t="n">
-        <v>8.6495</v>
+        <v>22.0724</v>
       </c>
       <c r="G38" t="n">
-        <v>1.98</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Commodity: Coffee</t>
+          <t>American: Invesco QQQ (QQQ)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1473,25 +1473,25 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="D39" t="n">
-        <v>-17.06</v>
+        <v>46.36</v>
       </c>
       <c r="E39" t="n">
-        <v>7.9805</v>
+        <v>24.5307</v>
       </c>
       <c r="F39" t="n">
-        <v>10.5478</v>
+        <v>32.3471</v>
       </c>
       <c r="G39" t="n">
-        <v>2.2</v>
+        <v>3.87</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Commodity: Coffee</t>
+          <t>American: Invesco QQQ (QQQ)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1500,25 +1500,25 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="D40" t="n">
-        <v>-17.06</v>
+        <v>46.36</v>
       </c>
       <c r="E40" t="n">
-        <v>11.5377</v>
+        <v>52.0533</v>
       </c>
       <c r="F40" t="n">
-        <v>13.8303</v>
+        <v>59.2239</v>
       </c>
       <c r="G40" t="n">
-        <v>3.46</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Commodity: Copper</t>
+          <t>American: Meta (META)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1527,25 +1527,25 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="D41" t="n">
-        <v>32.19</v>
+        <v>2.26</v>
       </c>
       <c r="E41" t="n">
-        <v>0.6228</v>
+        <v>11.6064</v>
       </c>
       <c r="F41" t="n">
-        <v>0.8149</v>
+        <v>16.8895</v>
       </c>
       <c r="G41" t="n">
-        <v>10.74</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Commodity: Copper</t>
+          <t>American: Meta (META)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1554,25 +1554,25 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="D42" t="n">
-        <v>32.19</v>
+        <v>2.26</v>
       </c>
       <c r="E42" t="n">
-        <v>0.45</v>
+        <v>12.5839</v>
       </c>
       <c r="F42" t="n">
-        <v>0.6783</v>
+        <v>18.7631</v>
       </c>
       <c r="G42" t="n">
-        <v>7.83</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Commodity: Copper</t>
+          <t>American: Meta (META)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1581,25 +1581,25 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="D43" t="n">
-        <v>32.15</v>
+        <v>2.26</v>
       </c>
       <c r="E43" t="n">
-        <v>0.5395</v>
+        <v>19.4521</v>
       </c>
       <c r="F43" t="n">
-        <v>0.7235</v>
+        <v>26.6685</v>
       </c>
       <c r="G43" t="n">
-        <v>9.51</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Commodity: Natural Gas</t>
+          <t>American: Microsoft (MSFT)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1608,25 +1608,25 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="D44" t="n">
-        <v>-21.95</v>
+        <v>-4.54</v>
       </c>
       <c r="E44" t="n">
-        <v>0.2929</v>
+        <v>8.089399999999999</v>
       </c>
       <c r="F44" t="n">
-        <v>0.5782</v>
+        <v>11.1107</v>
       </c>
       <c r="G44" t="n">
-        <v>6.51</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Commodity: Natural Gas</t>
+          <t>American: Microsoft (MSFT)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1635,25 +1635,25 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="D45" t="n">
-        <v>-21.95</v>
+        <v>-4.54</v>
       </c>
       <c r="E45" t="n">
-        <v>0.2669</v>
+        <v>8.457000000000001</v>
       </c>
       <c r="F45" t="n">
-        <v>0.5204</v>
+        <v>11.6514</v>
       </c>
       <c r="G45" t="n">
-        <v>6.13</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Commodity: Natural Gas</t>
+          <t>American: Microsoft (MSFT)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1662,25 +1662,25 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="D46" t="n">
-        <v>-21.95</v>
+        <v>-4.54</v>
       </c>
       <c r="E46" t="n">
-        <v>0.2222</v>
+        <v>9.7262</v>
       </c>
       <c r="F46" t="n">
-        <v>0.4634</v>
+        <v>12.7022</v>
       </c>
       <c r="G46" t="n">
-        <v>5.49</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Commodity: Sugar</t>
+          <t>American: Netflix (NFLX)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1689,25 +1689,25 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="D47" t="n">
-        <v>-20.82</v>
+        <v>-23.55</v>
       </c>
       <c r="E47" t="n">
-        <v>0.3388</v>
+        <v>2.4461</v>
       </c>
       <c r="F47" t="n">
-        <v>0.3967</v>
+        <v>3.2643</v>
       </c>
       <c r="G47" t="n">
-        <v>2.31</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Commodity: Sugar</t>
+          <t>American: Netflix (NFLX)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1716,25 +1716,25 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="D48" t="n">
-        <v>-20.82</v>
+        <v>-23.55</v>
       </c>
       <c r="E48" t="n">
-        <v>1.1678</v>
+        <v>2.5859</v>
       </c>
       <c r="F48" t="n">
-        <v>1.3238</v>
+        <v>3.5431</v>
       </c>
       <c r="G48" t="n">
-        <v>8.029999999999999</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Commodity: Sugar</t>
+          <t>American: Netflix (NFLX)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1743,25 +1743,25 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="D49" t="n">
-        <v>-20.82</v>
+        <v>-23.55</v>
       </c>
       <c r="E49" t="n">
-        <v>0.8534</v>
+        <v>2.4657</v>
       </c>
       <c r="F49" t="n">
-        <v>1.0488</v>
+        <v>3.4226</v>
       </c>
       <c r="G49" t="n">
-        <v>5.82</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Commodity: WTI Crude Oil</t>
+          <t>American: Nvidia (NVDA)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1770,25 +1770,25 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="D50" t="n">
-        <v>48.32</v>
+        <v>83.39</v>
       </c>
       <c r="E50" t="n">
-        <v>5.792</v>
+        <v>5.3283</v>
       </c>
       <c r="F50" t="n">
-        <v>9.5406</v>
+        <v>7.387</v>
       </c>
       <c r="G50" t="n">
-        <v>6.62</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Commodity: WTI Crude Oil</t>
+          <t>American: Nvidia (NVDA)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1797,25 +1797,25 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="D51" t="n">
-        <v>48.79</v>
+        <v>83.39</v>
       </c>
       <c r="E51" t="n">
-        <v>3.4193</v>
+        <v>7.2594</v>
       </c>
       <c r="F51" t="n">
-        <v>5.6688</v>
+        <v>10.3405</v>
       </c>
       <c r="G51" t="n">
-        <v>4.35</v>
+        <v>3.73</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Commodity: WTI Crude Oil</t>
+          <t>American: Nvidia (NVDA)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1824,25 +1824,25 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="D52" t="n">
-        <v>48.75</v>
+        <v>83.39</v>
       </c>
       <c r="E52" t="n">
-        <v>2.3312</v>
+        <v>15.6079</v>
       </c>
       <c r="F52" t="n">
-        <v>3.5324</v>
+        <v>18.3904</v>
       </c>
       <c r="G52" t="n">
-        <v>3.21</v>
+        <v>8.220000000000001</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Indian: Asian Paints</t>
+          <t>American: PepsiCo (PEP)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1851,25 +1851,25 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>494</v>
+        <v>501</v>
       </c>
       <c r="D53" t="n">
-        <v>0.92</v>
+        <v>22.36</v>
       </c>
       <c r="E53" t="n">
-        <v>36.9373</v>
+        <v>1.8391</v>
       </c>
       <c r="F53" t="n">
-        <v>50.5513</v>
+        <v>2.6729</v>
       </c>
       <c r="G53" t="n">
-        <v>1.47</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Indian: Asian Paints</t>
+          <t>American: PepsiCo (PEP)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1878,25 +1878,25 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>740</v>
+        <v>753</v>
       </c>
       <c r="D54" t="n">
-        <v>0.92</v>
+        <v>22.36</v>
       </c>
       <c r="E54" t="n">
-        <v>38.9029</v>
+        <v>1.8095</v>
       </c>
       <c r="F54" t="n">
-        <v>56.9923</v>
+        <v>2.5504</v>
       </c>
       <c r="G54" t="n">
-        <v>1.53</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Indian: Asian Paints</t>
+          <t>American: PepsiCo (PEP)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1905,25 +1905,25 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>987</v>
+        <v>1004</v>
       </c>
       <c r="D55" t="n">
-        <v>0.92</v>
+        <v>22.36</v>
       </c>
       <c r="E55" t="n">
-        <v>36.4575</v>
+        <v>1.7554</v>
       </c>
       <c r="F55" t="n">
-        <v>47.6685</v>
+        <v>2.3412</v>
       </c>
       <c r="G55" t="n">
-        <v>1.46</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Indian: Axis Bank</t>
+          <t>American: Qualcomm (QCOM)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1932,25 +1932,25 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>494</v>
+        <v>501</v>
       </c>
       <c r="D56" t="n">
-        <v>24.14</v>
+        <v>54.53</v>
       </c>
       <c r="E56" t="n">
-        <v>40.7941</v>
+        <v>7.0489</v>
       </c>
       <c r="F56" t="n">
-        <v>57.9817</v>
+        <v>9.5</v>
       </c>
       <c r="G56" t="n">
-        <v>3.07</v>
+        <v>4.71</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Indian: Axis Bank</t>
+          <t>American: Qualcomm (QCOM)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1959,25 +1959,25 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>740</v>
+        <v>753</v>
       </c>
       <c r="D57" t="n">
-        <v>24.14</v>
+        <v>54.53</v>
       </c>
       <c r="E57" t="n">
-        <v>33.0416</v>
+        <v>4.5319</v>
       </c>
       <c r="F57" t="n">
-        <v>49.7394</v>
+        <v>6.9767</v>
       </c>
       <c r="G57" t="n">
-        <v>2.53</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Indian: Axis Bank</t>
+          <t>American: Qualcomm (QCOM)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1986,25 +1986,25 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>987</v>
+        <v>1004</v>
       </c>
       <c r="D58" t="n">
-        <v>24.14</v>
+        <v>54.53</v>
       </c>
       <c r="E58" t="n">
-        <v>26.2278</v>
+        <v>3.8005</v>
       </c>
       <c r="F58" t="n">
-        <v>41.3134</v>
+        <v>6.1279</v>
       </c>
       <c r="G58" t="n">
-        <v>2.05</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Indian: Bajaj Finance</t>
+          <t>American: Salesforce (CRM)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2013,25 +2013,25 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>494</v>
+        <v>501</v>
       </c>
       <c r="D59" t="n">
-        <v>-6.44</v>
+        <v>-34.52</v>
       </c>
       <c r="E59" t="n">
-        <v>24.8579</v>
+        <v>31.7029</v>
       </c>
       <c r="F59" t="n">
-        <v>34.0842</v>
+        <v>37.0193</v>
       </c>
       <c r="G59" t="n">
-        <v>1.31</v>
+        <v>16.91</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Indian: Bajaj Finance</t>
+          <t>American: Salesforce (CRM)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2040,25 +2040,25 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>740</v>
+        <v>753</v>
       </c>
       <c r="D60" t="n">
-        <v>-6.44</v>
+        <v>-34.52</v>
       </c>
       <c r="E60" t="n">
-        <v>43.5003</v>
+        <v>10.2452</v>
       </c>
       <c r="F60" t="n">
-        <v>56.6693</v>
+        <v>13.4602</v>
       </c>
       <c r="G60" t="n">
-        <v>2.16</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Indian: Bajaj Finance</t>
+          <t>American: Salesforce (CRM)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2067,25 +2067,25 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>987</v>
+        <v>1004</v>
       </c>
       <c r="D61" t="n">
-        <v>-6.44</v>
+        <v>-34.52</v>
       </c>
       <c r="E61" t="n">
-        <v>37.7767</v>
+        <v>4.8549</v>
       </c>
       <c r="F61" t="n">
-        <v>49.8456</v>
+        <v>6.2874</v>
       </c>
       <c r="G61" t="n">
-        <v>1.88</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Indian: Coal India</t>
+          <t>American: ServiceNow (NOW)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2094,25 +2094,25 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>494</v>
+        <v>501</v>
       </c>
       <c r="D62" t="n">
-        <v>20.94</v>
+        <v>-53.22</v>
       </c>
       <c r="E62" t="n">
-        <v>6.2039</v>
+        <v>30.2577</v>
       </c>
       <c r="F62" t="n">
-        <v>8.389099999999999</v>
+        <v>35.2049</v>
       </c>
       <c r="G62" t="n">
-        <v>1.46</v>
+        <v>29.77</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Indian: Coal India</t>
+          <t>American: ServiceNow (NOW)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2121,25 +2121,25 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>740</v>
+        <v>753</v>
       </c>
       <c r="D63" t="n">
-        <v>20.94</v>
+        <v>-53.22</v>
       </c>
       <c r="E63" t="n">
-        <v>5.2278</v>
+        <v>5.124</v>
       </c>
       <c r="F63" t="n">
-        <v>7.3914</v>
+        <v>7.1843</v>
       </c>
       <c r="G63" t="n">
-        <v>1.26</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Indian: Coal India</t>
+          <t>American: ServiceNow (NOW)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2148,25 +2148,25 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>987</v>
+        <v>1004</v>
       </c>
       <c r="D64" t="n">
-        <v>20.94</v>
+        <v>-53.22</v>
       </c>
       <c r="E64" t="n">
-        <v>4.5159</v>
+        <v>3.6253</v>
       </c>
       <c r="F64" t="n">
-        <v>6.5047</v>
+        <v>4.9279</v>
       </c>
       <c r="G64" t="n">
-        <v>1.12</v>
+        <v>2.76</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Indian: Divi's Laboratories</t>
+          <t>American: Tesla (TSLA)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2175,25 +2175,25 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>494</v>
+        <v>501</v>
       </c>
       <c r="D65" t="n">
-        <v>11.21</v>
+        <v>50.39</v>
       </c>
       <c r="E65" t="n">
-        <v>75.3642</v>
+        <v>11.7703</v>
       </c>
       <c r="F65" t="n">
-        <v>96.86750000000001</v>
+        <v>16.6129</v>
       </c>
       <c r="G65" t="n">
-        <v>1.21</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Indian: Divi's Laboratories</t>
+          <t>American: Tesla (TSLA)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2202,25 +2202,25 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>740</v>
+        <v>753</v>
       </c>
       <c r="D66" t="n">
-        <v>11.21</v>
+        <v>50.39</v>
       </c>
       <c r="E66" t="n">
-        <v>82.62569999999999</v>
+        <v>12.6592</v>
       </c>
       <c r="F66" t="n">
-        <v>108.8699</v>
+        <v>18.0889</v>
       </c>
       <c r="G66" t="n">
-        <v>1.32</v>
+        <v>2.92</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Indian: Divi's Laboratories</t>
+          <t>American: Tesla (TSLA)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2229,25 +2229,25 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>987</v>
+        <v>1004</v>
       </c>
       <c r="D67" t="n">
-        <v>11.21</v>
+        <v>50.39</v>
       </c>
       <c r="E67" t="n">
-        <v>139.7913</v>
+        <v>14.7359</v>
       </c>
       <c r="F67" t="n">
-        <v>171.2463</v>
+        <v>19.7999</v>
       </c>
       <c r="G67" t="n">
-        <v>2.21</v>
+        <v>3.47</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Indian: HCL Technologies</t>
+          <t>American: Walmart (WMT)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2256,25 +2256,25 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>494</v>
+        <v>501</v>
       </c>
       <c r="D68" t="n">
-        <v>4.04</v>
+        <v>35.32</v>
       </c>
       <c r="E68" t="n">
-        <v>19.3475</v>
+        <v>8.696400000000001</v>
       </c>
       <c r="F68" t="n">
-        <v>25.4686</v>
+        <v>10.0034</v>
       </c>
       <c r="G68" t="n">
-        <v>1.28</v>
+        <v>6.91</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Indian: HCL Technologies</t>
+          <t>American: Walmart (WMT)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2283,25 +2283,25 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>740</v>
+        <v>753</v>
       </c>
       <c r="D69" t="n">
-        <v>4.04</v>
+        <v>35.32</v>
       </c>
       <c r="E69" t="n">
-        <v>18.6461</v>
+        <v>16.4717</v>
       </c>
       <c r="F69" t="n">
-        <v>24.0771</v>
+        <v>19.294</v>
       </c>
       <c r="G69" t="n">
-        <v>1.24</v>
+        <v>13.43</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Indian: HCL Technologies</t>
+          <t>American: Walmart (WMT)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2310,25 +2310,25 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>987</v>
+        <v>1004</v>
       </c>
       <c r="D70" t="n">
-        <v>4.04</v>
+        <v>35.32</v>
       </c>
       <c r="E70" t="n">
-        <v>18.7435</v>
+        <v>14.4664</v>
       </c>
       <c r="F70" t="n">
-        <v>24.99</v>
+        <v>18.4554</v>
       </c>
       <c r="G70" t="n">
-        <v>1.25</v>
+        <v>11.95</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Indian: HDFC Bank</t>
+          <t>Commodity: Brent Crude Oil</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2337,25 +2337,25 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="D71" t="n">
-        <v>-11.36</v>
+        <v>61.98</v>
       </c>
       <c r="E71" t="n">
-        <v>12.6078</v>
+        <v>9.9109</v>
       </c>
       <c r="F71" t="n">
-        <v>17.6035</v>
+        <v>14.0877</v>
       </c>
       <c r="G71" t="n">
-        <v>1.46</v>
+        <v>9.890000000000001</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Indian: HDFC Bank</t>
+          <t>Commodity: Brent Crude Oil</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2364,25 +2364,25 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>740</v>
+        <v>755</v>
       </c>
       <c r="D72" t="n">
-        <v>-11.36</v>
+        <v>61.98</v>
       </c>
       <c r="E72" t="n">
-        <v>9.5374</v>
+        <v>5.5997</v>
       </c>
       <c r="F72" t="n">
-        <v>13.3855</v>
+        <v>8.9841</v>
       </c>
       <c r="G72" t="n">
-        <v>1.07</v>
+        <v>5.98</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Indian: HDFC Bank</t>
+          <t>Commodity: Brent Crude Oil</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2391,25 +2391,25 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>987</v>
+        <v>1006</v>
       </c>
       <c r="D73" t="n">
-        <v>-11.36</v>
+        <v>61.92</v>
       </c>
       <c r="E73" t="n">
-        <v>21.714</v>
+        <v>2.5163</v>
       </c>
       <c r="F73" t="n">
-        <v>26.0681</v>
+        <v>3.7103</v>
       </c>
       <c r="G73" t="n">
-        <v>2.26</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Indian: ICICI Bank</t>
+          <t>Commodity: Coffee</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2418,25 +2418,25 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>494</v>
+        <v>501</v>
       </c>
       <c r="D74" t="n">
-        <v>1.96</v>
+        <v>-27.06</v>
       </c>
       <c r="E74" t="n">
-        <v>16.4491</v>
+        <v>6.2466</v>
       </c>
       <c r="F74" t="n">
-        <v>21.0454</v>
+        <v>8.335800000000001</v>
       </c>
       <c r="G74" t="n">
-        <v>1.23</v>
+        <v>1.97</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Indian: ICICI Bank</t>
+          <t>Commodity: Coffee</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2445,25 +2445,25 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>740</v>
+        <v>754</v>
       </c>
       <c r="D75" t="n">
-        <v>1.96</v>
+        <v>-27.06</v>
       </c>
       <c r="E75" t="n">
-        <v>23.7764</v>
+        <v>6.7406</v>
       </c>
       <c r="F75" t="n">
-        <v>29.4669</v>
+        <v>8.5229</v>
       </c>
       <c r="G75" t="n">
-        <v>1.76</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Indian: ICICI Bank</t>
+          <t>Commodity: Coffee</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2472,25 +2472,25 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>987</v>
+        <v>1005</v>
       </c>
       <c r="D76" t="n">
-        <v>1.96</v>
+        <v>-27.06</v>
       </c>
       <c r="E76" t="n">
-        <v>24.299</v>
+        <v>8.267200000000001</v>
       </c>
       <c r="F76" t="n">
-        <v>30.6995</v>
+        <v>10.796</v>
       </c>
       <c r="G76" t="n">
-        <v>1.78</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Indian: Infosys</t>
+          <t>Commodity: Copper</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2499,25 +2499,25 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="D77" t="n">
-        <v>-9.44</v>
+        <v>37.93</v>
       </c>
       <c r="E77" t="n">
-        <v>45.44</v>
+        <v>0.8498</v>
       </c>
       <c r="F77" t="n">
-        <v>61.0147</v>
+        <v>1.0041</v>
       </c>
       <c r="G77" t="n">
-        <v>3.34</v>
+        <v>14.44</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Indian: Infosys</t>
+          <t>Commodity: Copper</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2526,25 +2526,25 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>740</v>
+        <v>755</v>
       </c>
       <c r="D78" t="n">
-        <v>-9.44</v>
+        <v>37.89</v>
       </c>
       <c r="E78" t="n">
-        <v>20.0149</v>
+        <v>0.6097</v>
       </c>
       <c r="F78" t="n">
-        <v>27.6094</v>
+        <v>0.83</v>
       </c>
       <c r="G78" t="n">
-        <v>1.36</v>
+        <v>10.44</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Indian: Infosys</t>
+          <t>Commodity: Copper</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2553,25 +2553,25 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>987</v>
+        <v>1006</v>
       </c>
       <c r="D79" t="n">
-        <v>-9.44</v>
+        <v>37.91</v>
       </c>
       <c r="E79" t="n">
-        <v>19.2567</v>
+        <v>0.1437</v>
       </c>
       <c r="F79" t="n">
-        <v>26.3095</v>
+        <v>0.2153</v>
       </c>
       <c r="G79" t="n">
-        <v>1.31</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Indian: Kotak Mahindra Bank</t>
+          <t>Commodity: Gold</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2580,25 +2580,25 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="D80" t="n">
-        <v>-12.68</v>
+        <v>45.34</v>
       </c>
       <c r="E80" t="n">
-        <v>5.58</v>
+        <v>604.3158</v>
       </c>
       <c r="F80" t="n">
-        <v>7.3925</v>
+        <v>664.0368999999999</v>
       </c>
       <c r="G80" t="n">
-        <v>1.37</v>
+        <v>12.39</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Indian: Kotak Mahindra Bank</t>
+          <t>Commodity: Gold</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2607,25 +2607,25 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>740</v>
+        <v>754</v>
       </c>
       <c r="D81" t="n">
-        <v>-12.68</v>
+        <v>45.33</v>
       </c>
       <c r="E81" t="n">
-        <v>5.6428</v>
+        <v>668.399</v>
       </c>
       <c r="F81" t="n">
-        <v>7.4308</v>
+        <v>771.6698</v>
       </c>
       <c r="G81" t="n">
-        <v>1.37</v>
+        <v>14.08</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Indian: Kotak Mahindra Bank</t>
+          <t>Commodity: Gold</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2634,25 +2634,25 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>987</v>
+        <v>1005</v>
       </c>
       <c r="D82" t="n">
-        <v>-12.68</v>
+        <v>45.34</v>
       </c>
       <c r="E82" t="n">
-        <v>5.7562</v>
+        <v>1001.8548</v>
       </c>
       <c r="F82" t="n">
-        <v>7.8291</v>
+        <v>1152.9255</v>
       </c>
       <c r="G82" t="n">
-        <v>1.41</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Indian: Larsen &amp; Toubro</t>
+          <t>Commodity: Natural Gas</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2661,25 +2661,25 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="D83" t="n">
-        <v>22.42</v>
+        <v>-23.37</v>
       </c>
       <c r="E83" t="n">
-        <v>124.9766</v>
+        <v>0.2327</v>
       </c>
       <c r="F83" t="n">
-        <v>163.1399</v>
+        <v>0.4996</v>
       </c>
       <c r="G83" t="n">
-        <v>3.09</v>
+        <v>5.56</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Indian: Larsen &amp; Toubro</t>
+          <t>Commodity: Natural Gas</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2688,25 +2688,25 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>740</v>
+        <v>755</v>
       </c>
       <c r="D84" t="n">
-        <v>22.42</v>
+        <v>-23.37</v>
       </c>
       <c r="E84" t="n">
-        <v>191.9581</v>
+        <v>0.2589</v>
       </c>
       <c r="F84" t="n">
-        <v>238.5675</v>
+        <v>0.5162</v>
       </c>
       <c r="G84" t="n">
-        <v>4.76</v>
+        <v>5.92</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Indian: Larsen &amp; Toubro</t>
+          <t>Commodity: Natural Gas</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2715,25 +2715,25 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>987</v>
+        <v>1006</v>
       </c>
       <c r="D85" t="n">
-        <v>22.42</v>
+        <v>-23.37</v>
       </c>
       <c r="E85" t="n">
-        <v>150.0257</v>
+        <v>0.218</v>
       </c>
       <c r="F85" t="n">
-        <v>206.3692</v>
+        <v>0.4667</v>
       </c>
       <c r="G85" t="n">
-        <v>3.74</v>
+        <v>5.42</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Indian: Maruti Suzuki</t>
+          <t>Commodity: Palladium</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2742,25 +2742,25 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>494</v>
+        <v>501</v>
       </c>
       <c r="D86" t="n">
-        <v>15.12</v>
+        <v>52.45</v>
       </c>
       <c r="E86" t="n">
-        <v>440.8436</v>
+        <v>190.8432</v>
       </c>
       <c r="F86" t="n">
-        <v>565.4906999999999</v>
+        <v>246.2726</v>
       </c>
       <c r="G86" t="n">
-        <v>2.99</v>
+        <v>10.72</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Indian: Maruti Suzuki</t>
+          <t>Commodity: Palladium</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2769,25 +2769,25 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>740</v>
+        <v>753</v>
       </c>
       <c r="D87" t="n">
-        <v>15.12</v>
+        <v>52.45</v>
       </c>
       <c r="E87" t="n">
-        <v>910.3939</v>
+        <v>210.5171</v>
       </c>
       <c r="F87" t="n">
-        <v>1056.3124</v>
+        <v>265.0127</v>
       </c>
       <c r="G87" t="n">
-        <v>5.76</v>
+        <v>12.35</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Indian: Maruti Suzuki</t>
+          <t>Commodity: Palladium</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2796,25 +2796,25 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>987</v>
+        <v>1004</v>
       </c>
       <c r="D88" t="n">
-        <v>15.12</v>
+        <v>52.45</v>
       </c>
       <c r="E88" t="n">
-        <v>2187.5429</v>
+        <v>50.2763</v>
       </c>
       <c r="F88" t="n">
-        <v>2622.8047</v>
+        <v>74.0817</v>
       </c>
       <c r="G88" t="n">
-        <v>13.88</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Indian: NTPC Limited</t>
+          <t>Commodity: Platinum</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2823,25 +2823,25 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="D89" t="n">
-        <v>13.14</v>
+        <v>109.8</v>
       </c>
       <c r="E89" t="n">
-        <v>5.1827</v>
+        <v>393.6422</v>
       </c>
       <c r="F89" t="n">
-        <v>6.8188</v>
+        <v>438.395</v>
       </c>
       <c r="G89" t="n">
-        <v>1.45</v>
+        <v>17.79</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Indian: NTPC Limited</t>
+          <t>Commodity: Platinum</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2850,25 +2850,25 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>740</v>
+        <v>754</v>
       </c>
       <c r="D90" t="n">
-        <v>13.14</v>
+        <v>109.8</v>
       </c>
       <c r="E90" t="n">
-        <v>4.2473</v>
+        <v>385.6182</v>
       </c>
       <c r="F90" t="n">
-        <v>5.6956</v>
+        <v>478.0886</v>
       </c>
       <c r="G90" t="n">
-        <v>1.21</v>
+        <v>17.91</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Indian: NTPC Limited</t>
+          <t>Commodity: Platinum</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2877,25 +2877,25 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>987</v>
+        <v>1005</v>
       </c>
       <c r="D91" t="n">
-        <v>13.14</v>
+        <v>109.8</v>
       </c>
       <c r="E91" t="n">
-        <v>3.7355</v>
+        <v>417.0647</v>
       </c>
       <c r="F91" t="n">
-        <v>5.172</v>
+        <v>533.5137</v>
       </c>
       <c r="G91" t="n">
-        <v>1.07</v>
+        <v>20.23</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Indian: Nestlé India</t>
+          <t>Commodity: Silver</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2904,25 +2904,25 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="D92" t="n">
-        <v>9.44</v>
+        <v>150.28</v>
       </c>
       <c r="E92" t="n">
-        <v>14.3623</v>
+        <v>17.3074</v>
       </c>
       <c r="F92" t="n">
-        <v>17.7525</v>
+        <v>19.8291</v>
       </c>
       <c r="G92" t="n">
-        <v>1.13</v>
+        <v>20.66</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Indian: Nestlé India</t>
+          <t>Commodity: Silver</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2931,25 +2931,25 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>740</v>
+        <v>754</v>
       </c>
       <c r="D93" t="n">
-        <v>9.44</v>
+        <v>150.28</v>
       </c>
       <c r="E93" t="n">
-        <v>14.741</v>
+        <v>23.4245</v>
       </c>
       <c r="F93" t="n">
-        <v>19.3028</v>
+        <v>28.1305</v>
       </c>
       <c r="G93" t="n">
-        <v>1.17</v>
+        <v>29.67</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Indian: Nestlé India</t>
+          <t>Commodity: Silver</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2958,25 +2958,25 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>987</v>
+        <v>1005</v>
       </c>
       <c r="D94" t="n">
-        <v>9.44</v>
+        <v>150.28</v>
       </c>
       <c r="E94" t="n">
-        <v>13.9284</v>
+        <v>24.876</v>
       </c>
       <c r="F94" t="n">
-        <v>18.5143</v>
+        <v>31.128</v>
       </c>
       <c r="G94" t="n">
-        <v>1.14</v>
+        <v>33.69</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Indian: Power Grid</t>
+          <t>Commodity: Sugar</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2985,25 +2985,25 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>494</v>
+        <v>501</v>
       </c>
       <c r="D95" t="n">
-        <v>5.53</v>
+        <v>-17.38</v>
       </c>
       <c r="E95" t="n">
-        <v>3.611</v>
+        <v>0.3301</v>
       </c>
       <c r="F95" t="n">
-        <v>5.0888</v>
+        <v>0.4161</v>
       </c>
       <c r="G95" t="n">
-        <v>1.3</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Indian: Power Grid</t>
+          <t>Commodity: Sugar</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3012,25 +3012,25 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>740</v>
+        <v>754</v>
       </c>
       <c r="D96" t="n">
-        <v>5.53</v>
+        <v>-17.38</v>
       </c>
       <c r="E96" t="n">
-        <v>3.0029</v>
+        <v>1.1313</v>
       </c>
       <c r="F96" t="n">
-        <v>4.2818</v>
+        <v>1.2623</v>
       </c>
       <c r="G96" t="n">
-        <v>1.08</v>
+        <v>7.87</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Indian: Power Grid</t>
+          <t>Commodity: Sugar</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3039,25 +3039,25 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>987</v>
+        <v>1005</v>
       </c>
       <c r="D97" t="n">
-        <v>5.53</v>
+        <v>-17.38</v>
       </c>
       <c r="E97" t="n">
-        <v>2.9954</v>
+        <v>1.1027</v>
       </c>
       <c r="F97" t="n">
-        <v>4.1268</v>
+        <v>1.3173</v>
       </c>
       <c r="G97" t="n">
-        <v>1.07</v>
+        <v>7.61</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Indian: Reliance Industries</t>
+          <t>Commodity: WTI Crude Oil</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3066,25 +3066,25 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="D98" t="n">
-        <v>9.6</v>
+        <v>61.18</v>
       </c>
       <c r="E98" t="n">
-        <v>17.8868</v>
+        <v>8.699299999999999</v>
       </c>
       <c r="F98" t="n">
-        <v>23.1633</v>
+        <v>12.3371</v>
       </c>
       <c r="G98" t="n">
-        <v>1.25</v>
+        <v>9.31</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Indian: Reliance Industries</t>
+          <t>Commodity: WTI Crude Oil</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3093,25 +3093,25 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>740</v>
+        <v>754</v>
       </c>
       <c r="D99" t="n">
-        <v>9.6</v>
+        <v>60.53</v>
       </c>
       <c r="E99" t="n">
-        <v>15.9453</v>
+        <v>4.6233</v>
       </c>
       <c r="F99" t="n">
-        <v>21.403</v>
+        <v>6.9844</v>
       </c>
       <c r="G99" t="n">
-        <v>1.11</v>
+        <v>5.53</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Indian: Reliance Industries</t>
+          <t>Commodity: WTI Crude Oil</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3120,25 +3120,25 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>987</v>
+        <v>1005</v>
       </c>
       <c r="D100" t="n">
-        <v>9.6</v>
+        <v>60.53</v>
       </c>
       <c r="E100" t="n">
-        <v>16.2722</v>
+        <v>2.7206</v>
       </c>
       <c r="F100" t="n">
-        <v>21.169</v>
+        <v>4.1977</v>
       </c>
       <c r="G100" t="n">
-        <v>1.14</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Indian: State Bank of India</t>
+          <t>Indian: Adani Green Energy</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3147,25 +3147,25 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D101" t="n">
-        <v>41.36</v>
+        <v>51.1</v>
       </c>
       <c r="E101" t="n">
-        <v>88.05840000000001</v>
+        <v>37.7862</v>
       </c>
       <c r="F101" t="n">
-        <v>120.0269</v>
+        <v>57.8197</v>
       </c>
       <c r="G101" t="n">
-        <v>7.87</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Indian: State Bank of India</t>
+          <t>Indian: Adani Green Energy</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3174,25 +3174,25 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="D102" t="n">
-        <v>41.36</v>
+        <v>51.06</v>
       </c>
       <c r="E102" t="n">
-        <v>148.5722</v>
+        <v>31.9246</v>
       </c>
       <c r="F102" t="n">
-        <v>180.453</v>
+        <v>45.6128</v>
       </c>
       <c r="G102" t="n">
-        <v>14.02</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Indian: State Bank of India</t>
+          <t>Indian: Adani Green Energy</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3201,25 +3201,25 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="D103" t="n">
-        <v>41.36</v>
+        <v>51.08</v>
       </c>
       <c r="E103" t="n">
-        <v>113.4408</v>
+        <v>23.7169</v>
       </c>
       <c r="F103" t="n">
-        <v>156.9793</v>
+        <v>34.6866</v>
       </c>
       <c r="G103" t="n">
-        <v>10.76</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Indian: Sun Pharmaceutical</t>
+          <t>Indian: Adani Ports</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3228,25 +3228,25 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D104" t="n">
-        <v>-2.4</v>
+        <v>32.01</v>
       </c>
       <c r="E104" t="n">
-        <v>17.3843</v>
+        <v>52.2236</v>
       </c>
       <c r="F104" t="n">
-        <v>22.5559</v>
+        <v>80.3883</v>
       </c>
       <c r="G104" t="n">
-        <v>1.01</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Indian: Sun Pharmaceutical</t>
+          <t>Indian: Adani Ports</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3255,25 +3255,25 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="D105" t="n">
-        <v>-2.4</v>
+        <v>32.01</v>
       </c>
       <c r="E105" t="n">
-        <v>16.1061</v>
+        <v>38.6458</v>
       </c>
       <c r="F105" t="n">
-        <v>21.343</v>
+        <v>65.4252</v>
       </c>
       <c r="G105" t="n">
-        <v>0.9399999999999999</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Indian: Sun Pharmaceutical</t>
+          <t>Indian: Adani Ports</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3282,25 +3282,25 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="D106" t="n">
-        <v>-2.4</v>
+        <v>32.01</v>
       </c>
       <c r="E106" t="n">
-        <v>16.2341</v>
+        <v>33.0384</v>
       </c>
       <c r="F106" t="n">
-        <v>21.4205</v>
+        <v>56.6938</v>
       </c>
       <c r="G106" t="n">
-        <v>0.96</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Indian: Tata Consultancy Services (TCS)</t>
+          <t>Indian: Asian Paints</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3309,25 +3309,25 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D107" t="n">
-        <v>-22.47</v>
+        <v>11.47</v>
       </c>
       <c r="E107" t="n">
-        <v>185.8197</v>
+        <v>37.4285</v>
       </c>
       <c r="F107" t="n">
-        <v>265.5477</v>
+        <v>48.5377</v>
       </c>
       <c r="G107" t="n">
-        <v>7.23</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Indian: Tata Consultancy Services (TCS)</t>
+          <t>Indian: Asian Paints</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3336,25 +3336,25 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="D108" t="n">
-        <v>-22.47</v>
+        <v>11.46</v>
       </c>
       <c r="E108" t="n">
-        <v>152.5683</v>
+        <v>38.541</v>
       </c>
       <c r="F108" t="n">
-        <v>245.7499</v>
+        <v>56.5471</v>
       </c>
       <c r="G108" t="n">
-        <v>5.89</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Indian: Tata Consultancy Services (TCS)</t>
+          <t>Indian: Asian Paints</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3363,25 +3363,25 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="D109" t="n">
-        <v>-22.47</v>
+        <v>11.43</v>
       </c>
       <c r="E109" t="n">
-        <v>68.6544</v>
+        <v>35.2965</v>
       </c>
       <c r="F109" t="n">
-        <v>113.5625</v>
+        <v>47.405</v>
       </c>
       <c r="G109" t="n">
-        <v>2.57</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Indian: Tata Steel</t>
+          <t>Indian: Axis Bank</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3390,25 +3390,25 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D110" t="n">
-        <v>50.44</v>
+        <v>9.91</v>
       </c>
       <c r="E110" t="n">
-        <v>10.9149</v>
+        <v>50.1522</v>
       </c>
       <c r="F110" t="n">
-        <v>14.4368</v>
+        <v>64.18980000000001</v>
       </c>
       <c r="G110" t="n">
-        <v>5.5</v>
+        <v>3.76</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Indian: Tata Steel</t>
+          <t>Indian: Axis Bank</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3417,25 +3417,25 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="D111" t="n">
-        <v>50.44</v>
+        <v>9.93</v>
       </c>
       <c r="E111" t="n">
-        <v>12.971</v>
+        <v>39.8771</v>
       </c>
       <c r="F111" t="n">
-        <v>17.8083</v>
+        <v>56.4383</v>
       </c>
       <c r="G111" t="n">
-        <v>6.64</v>
+        <v>3.02</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Indian: Tata Steel</t>
+          <t>Indian: Axis Bank</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3444,25 +3444,25 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="D112" t="n">
-        <v>50.44</v>
+        <v>9.94</v>
       </c>
       <c r="E112" t="n">
-        <v>9.883900000000001</v>
+        <v>30.6199</v>
       </c>
       <c r="F112" t="n">
-        <v>14.945</v>
+        <v>45.9761</v>
       </c>
       <c r="G112" t="n">
-        <v>5.12</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Indian: Titan Company</t>
+          <t>Indian: BPCL</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3471,25 +3471,25 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D113" t="n">
-        <v>44.75</v>
+        <v>-0.03</v>
       </c>
       <c r="E113" t="n">
-        <v>237.7835</v>
+        <v>9.7959</v>
       </c>
       <c r="F113" t="n">
-        <v>293.26</v>
+        <v>12.6337</v>
       </c>
       <c r="G113" t="n">
-        <v>5.67</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Indian: Titan Company</t>
+          <t>Indian: BPCL</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3498,25 +3498,25 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="D114" t="n">
-        <v>44.75</v>
+        <v>-0.05</v>
       </c>
       <c r="E114" t="n">
-        <v>266.6697</v>
+        <v>23.9575</v>
       </c>
       <c r="F114" t="n">
-        <v>343.439</v>
+        <v>30.0995</v>
       </c>
       <c r="G114" t="n">
-        <v>6.47</v>
+        <v>6.71</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Indian: Titan Company</t>
+          <t>Indian: BPCL</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3525,25 +3525,25 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="D115" t="n">
-        <v>44.75</v>
+        <v>0</v>
       </c>
       <c r="E115" t="n">
-        <v>201.4902</v>
+        <v>19.026</v>
       </c>
       <c r="F115" t="n">
-        <v>288.9926</v>
+        <v>26.4002</v>
       </c>
       <c r="G115" t="n">
-        <v>4.92</v>
+        <v>5.37</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Indian: UltraTech Cement</t>
+          <t>Indian: Bajaj Finance</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3552,25 +3552,25 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D116" t="n">
-        <v>0.66</v>
+        <v>-10.92</v>
       </c>
       <c r="E116" t="n">
-        <v>195.4181</v>
+        <v>24.1944</v>
       </c>
       <c r="F116" t="n">
-        <v>252.2347</v>
+        <v>34.0867</v>
       </c>
       <c r="G116" t="n">
-        <v>1.65</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Indian: UltraTech Cement</t>
+          <t>Indian: Bajaj Finance</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3579,25 +3579,25 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="D117" t="n">
-        <v>0.66</v>
+        <v>-10.9</v>
       </c>
       <c r="E117" t="n">
-        <v>177.7661</v>
+        <v>33.2755</v>
       </c>
       <c r="F117" t="n">
-        <v>235.1395</v>
+        <v>45.2582</v>
       </c>
       <c r="G117" t="n">
-        <v>1.49</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Indian: UltraTech Cement</t>
+          <t>Indian: Bajaj Finance</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3606,25 +3606,25 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="D118" t="n">
-        <v>0.66</v>
+        <v>-10.9</v>
       </c>
       <c r="E118" t="n">
-        <v>468.8169</v>
+        <v>35.6645</v>
       </c>
       <c r="F118" t="n">
-        <v>579.2191</v>
+        <v>48.3739</v>
       </c>
       <c r="G118" t="n">
-        <v>3.79</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Indian: Wipro</t>
+          <t>Indian: Bharti Airtel</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3633,25 +3633,25 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D119" t="n">
-        <v>-13.8</v>
+        <v>-6.24</v>
       </c>
       <c r="E119" t="n">
-        <v>9.058400000000001</v>
+        <v>23.6804</v>
       </c>
       <c r="F119" t="n">
-        <v>12.7183</v>
+        <v>30.4441</v>
       </c>
       <c r="G119" t="n">
-        <v>4.41</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Indian: Wipro</t>
+          <t>Indian: Bharti Airtel</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3660,46 +3660,2071 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="D120" t="n">
-        <v>-13.8</v>
+        <v>-6.25</v>
       </c>
       <c r="E120" t="n">
-        <v>3.1326</v>
+        <v>61.0308</v>
       </c>
       <c r="F120" t="n">
-        <v>4.3057</v>
+        <v>79.3612</v>
       </c>
       <c r="G120" t="n">
-        <v>1.38</v>
+        <v>2.98</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
+          <t>Indian: Bharti Airtel</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>4y</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>989</v>
+      </c>
+      <c r="D121" t="n">
+        <v>-6.26</v>
+      </c>
+      <c r="E121" t="n">
+        <v>52.4115</v>
+      </c>
+      <c r="F121" t="n">
+        <v>71.39879999999999</v>
+      </c>
+      <c r="G121" t="n">
+        <v>2.59</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Indian: Coal India</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>2y</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>495</v>
+      </c>
+      <c r="D122" t="n">
+        <v>29.75</v>
+      </c>
+      <c r="E122" t="n">
+        <v>8.223000000000001</v>
+      </c>
+      <c r="F122" t="n">
+        <v>11.0434</v>
+      </c>
+      <c r="G122" t="n">
+        <v>1.89</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Indian: Coal India</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>3y</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>741</v>
+      </c>
+      <c r="D123" t="n">
+        <v>29.77</v>
+      </c>
+      <c r="E123" t="n">
+        <v>5.8234</v>
+      </c>
+      <c r="F123" t="n">
+        <v>7.9258</v>
+      </c>
+      <c r="G123" t="n">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Indian: Coal India</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>4y</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>989</v>
+      </c>
+      <c r="D124" t="n">
+        <v>29.77</v>
+      </c>
+      <c r="E124" t="n">
+        <v>5.0459</v>
+      </c>
+      <c r="F124" t="n">
+        <v>7.0659</v>
+      </c>
+      <c r="G124" t="n">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Indian: Divi's Laboratories</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>2y</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>494</v>
+      </c>
+      <c r="D125" t="n">
+        <v>10.08</v>
+      </c>
+      <c r="E125" t="n">
+        <v>76.2701</v>
+      </c>
+      <c r="F125" t="n">
+        <v>97.37130000000001</v>
+      </c>
+      <c r="G125" t="n">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Indian: Divi's Laboratories</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>3y</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>740</v>
+      </c>
+      <c r="D126" t="n">
+        <v>10.07</v>
+      </c>
+      <c r="E126" t="n">
+        <v>80.1461</v>
+      </c>
+      <c r="F126" t="n">
+        <v>105.0764</v>
+      </c>
+      <c r="G126" t="n">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Indian: Divi's Laboratories</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>4y</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>988</v>
+      </c>
+      <c r="D127" t="n">
+        <v>10.07</v>
+      </c>
+      <c r="E127" t="n">
+        <v>110.9413</v>
+      </c>
+      <c r="F127" t="n">
+        <v>140.3149</v>
+      </c>
+      <c r="G127" t="n">
+        <v>1.78</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Indian: GAIL (India)</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2y</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>495</v>
+      </c>
+      <c r="D128" t="n">
+        <v>-10.51</v>
+      </c>
+      <c r="E128" t="n">
+        <v>4.1566</v>
+      </c>
+      <c r="F128" t="n">
+        <v>6.1491</v>
+      </c>
+      <c r="G128" t="n">
+        <v>2.77</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Indian: GAIL (India)</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>3y</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>741</v>
+      </c>
+      <c r="D129" t="n">
+        <v>-10.51</v>
+      </c>
+      <c r="E129" t="n">
+        <v>2.6293</v>
+      </c>
+      <c r="F129" t="n">
+        <v>3.5651</v>
+      </c>
+      <c r="G129" t="n">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Indian: GAIL (India)</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>4y</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>989</v>
+      </c>
+      <c r="D130" t="n">
+        <v>-10.54</v>
+      </c>
+      <c r="E130" t="n">
+        <v>2.4528</v>
+      </c>
+      <c r="F130" t="n">
+        <v>3.3816</v>
+      </c>
+      <c r="G130" t="n">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Indian: HCL Technologies</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>2y</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>495</v>
+      </c>
+      <c r="D131" t="n">
+        <v>-19.98</v>
+      </c>
+      <c r="E131" t="n">
+        <v>29.3325</v>
+      </c>
+      <c r="F131" t="n">
+        <v>42.1668</v>
+      </c>
+      <c r="G131" t="n">
+        <v>2.18</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Indian: HCL Technologies</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>3y</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>741</v>
+      </c>
+      <c r="D132" t="n">
+        <v>-20.01</v>
+      </c>
+      <c r="E132" t="n">
+        <v>20.3477</v>
+      </c>
+      <c r="F132" t="n">
+        <v>29.3234</v>
+      </c>
+      <c r="G132" t="n">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Indian: HCL Technologies</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>4y</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>989</v>
+      </c>
+      <c r="D133" t="n">
+        <v>-19.99</v>
+      </c>
+      <c r="E133" t="n">
+        <v>19.2214</v>
+      </c>
+      <c r="F133" t="n">
+        <v>27.3366</v>
+      </c>
+      <c r="G133" t="n">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Indian: HDFC Bank</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2y</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>495</v>
+      </c>
+      <c r="D134" t="n">
+        <v>-19.79</v>
+      </c>
+      <c r="E134" t="n">
+        <v>14.7174</v>
+      </c>
+      <c r="F134" t="n">
+        <v>19.1613</v>
+      </c>
+      <c r="G134" t="n">
+        <v>1.76</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Indian: HDFC Bank</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>3y</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>741</v>
+      </c>
+      <c r="D135" t="n">
+        <v>-19.79</v>
+      </c>
+      <c r="E135" t="n">
+        <v>10.4737</v>
+      </c>
+      <c r="F135" t="n">
+        <v>14.1508</v>
+      </c>
+      <c r="G135" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Indian: HDFC Bank</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>4y</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>989</v>
+      </c>
+      <c r="D136" t="n">
+        <v>-19.78</v>
+      </c>
+      <c r="E136" t="n">
+        <v>10.4159</v>
+      </c>
+      <c r="F136" t="n">
+        <v>13.7544</v>
+      </c>
+      <c r="G136" t="n">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Indian: Hindustan Unilever</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>2y</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>495</v>
+      </c>
+      <c r="D137" t="n">
+        <v>-2.02</v>
+      </c>
+      <c r="E137" t="n">
+        <v>35.0054</v>
+      </c>
+      <c r="F137" t="n">
+        <v>45.4904</v>
+      </c>
+      <c r="G137" t="n">
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Indian: Hindustan Unilever</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>3y</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>741</v>
+      </c>
+      <c r="D138" t="n">
+        <v>-1.98</v>
+      </c>
+      <c r="E138" t="n">
+        <v>28.9704</v>
+      </c>
+      <c r="F138" t="n">
+        <v>38.57</v>
+      </c>
+      <c r="G138" t="n">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Indian: Hindustan Unilever</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>4y</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>989</v>
+      </c>
+      <c r="D139" t="n">
+        <v>-1.98</v>
+      </c>
+      <c r="E139" t="n">
+        <v>26.4213</v>
+      </c>
+      <c r="F139" t="n">
+        <v>34.0426</v>
+      </c>
+      <c r="G139" t="n">
+        <v>1.11</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Indian: ICICI Bank</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>2y</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>495</v>
+      </c>
+      <c r="D140" t="n">
+        <v>-10.79</v>
+      </c>
+      <c r="E140" t="n">
+        <v>17.8654</v>
+      </c>
+      <c r="F140" t="n">
+        <v>22.2754</v>
+      </c>
+      <c r="G140" t="n">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Indian: ICICI Bank</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>3y</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>741</v>
+      </c>
+      <c r="D141" t="n">
+        <v>-10.79</v>
+      </c>
+      <c r="E141" t="n">
+        <v>16.5069</v>
+      </c>
+      <c r="F141" t="n">
+        <v>20.8563</v>
+      </c>
+      <c r="G141" t="n">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Indian: ICICI Bank</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>4y</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>989</v>
+      </c>
+      <c r="D142" t="n">
+        <v>-10.79</v>
+      </c>
+      <c r="E142" t="n">
+        <v>22.4614</v>
+      </c>
+      <c r="F142" t="n">
+        <v>28.72</v>
+      </c>
+      <c r="G142" t="n">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Indian: Indian Oil</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>2y</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>495</v>
+      </c>
+      <c r="D143" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="E143" t="n">
+        <v>3.9893</v>
+      </c>
+      <c r="F143" t="n">
+        <v>5.8691</v>
+      </c>
+      <c r="G143" t="n">
+        <v>2.43</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Indian: Indian Oil</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>3y</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>741</v>
+      </c>
+      <c r="D144" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="E144" t="n">
+        <v>3.5242</v>
+      </c>
+      <c r="F144" t="n">
+        <v>5.1483</v>
+      </c>
+      <c r="G144" t="n">
+        <v>2.19</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Indian: Indian Oil</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>4y</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>989</v>
+      </c>
+      <c r="D145" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="E145" t="n">
+        <v>2.9478</v>
+      </c>
+      <c r="F145" t="n">
+        <v>4.475</v>
+      </c>
+      <c r="G145" t="n">
+        <v>1.87</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Indian: Infosys</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>2y</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>495</v>
+      </c>
+      <c r="D146" t="n">
+        <v>-19.12</v>
+      </c>
+      <c r="E146" t="n">
+        <v>83.6061</v>
+      </c>
+      <c r="F146" t="n">
+        <v>107.9512</v>
+      </c>
+      <c r="G146" t="n">
+        <v>6.53</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Indian: Infosys</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>3y</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>741</v>
+      </c>
+      <c r="D147" t="n">
+        <v>-19.12</v>
+      </c>
+      <c r="E147" t="n">
+        <v>23.5754</v>
+      </c>
+      <c r="F147" t="n">
+        <v>32.4258</v>
+      </c>
+      <c r="G147" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Indian: Infosys</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>4y</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>989</v>
+      </c>
+      <c r="D148" t="n">
+        <v>-19.12</v>
+      </c>
+      <c r="E148" t="n">
+        <v>19.8174</v>
+      </c>
+      <c r="F148" t="n">
+        <v>27.2235</v>
+      </c>
+      <c r="G148" t="n">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Indian: Kotak Mahindra Bank</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>2y</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>495</v>
+      </c>
+      <c r="D149" t="n">
+        <v>-8.779999999999999</v>
+      </c>
+      <c r="E149" t="n">
+        <v>5.613</v>
+      </c>
+      <c r="F149" t="n">
+        <v>7.3858</v>
+      </c>
+      <c r="G149" t="n">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Indian: Kotak Mahindra Bank</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>3y</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>741</v>
+      </c>
+      <c r="D150" t="n">
+        <v>-8.779999999999999</v>
+      </c>
+      <c r="E150" t="n">
+        <v>5.1905</v>
+      </c>
+      <c r="F150" t="n">
+        <v>6.8732</v>
+      </c>
+      <c r="G150" t="n">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Indian: Kotak Mahindra Bank</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>4y</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>989</v>
+      </c>
+      <c r="D151" t="n">
+        <v>-8.779999999999999</v>
+      </c>
+      <c r="E151" t="n">
+        <v>5.4517</v>
+      </c>
+      <c r="F151" t="n">
+        <v>7.4184</v>
+      </c>
+      <c r="G151" t="n">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Indian: Larsen &amp; Toubro</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>2y</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>495</v>
+      </c>
+      <c r="D152" t="n">
+        <v>19.34</v>
+      </c>
+      <c r="E152" t="n">
+        <v>107.2212</v>
+      </c>
+      <c r="F152" t="n">
+        <v>143.0479</v>
+      </c>
+      <c r="G152" t="n">
+        <v>2.66</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Indian: Larsen &amp; Toubro</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>3y</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>741</v>
+      </c>
+      <c r="D153" t="n">
+        <v>19.32</v>
+      </c>
+      <c r="E153" t="n">
+        <v>216.0807</v>
+      </c>
+      <c r="F153" t="n">
+        <v>251.9869</v>
+      </c>
+      <c r="G153" t="n">
+        <v>5.34</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Indian: Larsen &amp; Toubro</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>4y</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>989</v>
+      </c>
+      <c r="D154" t="n">
+        <v>19.33</v>
+      </c>
+      <c r="E154" t="n">
+        <v>170.189</v>
+      </c>
+      <c r="F154" t="n">
+        <v>218.4633</v>
+      </c>
+      <c r="G154" t="n">
+        <v>4.23</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Indian: Mahindra &amp; Mahindra</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>2y</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>495</v>
+      </c>
+      <c r="D155" t="n">
+        <v>5.41</v>
+      </c>
+      <c r="E155" t="n">
+        <v>69.146</v>
+      </c>
+      <c r="F155" t="n">
+        <v>94.4081</v>
+      </c>
+      <c r="G155" t="n">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Indian: Mahindra &amp; Mahindra</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>3y</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>741</v>
+      </c>
+      <c r="D156" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="E156" t="n">
+        <v>88.77</v>
+      </c>
+      <c r="F156" t="n">
+        <v>111.4275</v>
+      </c>
+      <c r="G156" t="n">
+        <v>2.55</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Indian: Mahindra &amp; Mahindra</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>4y</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>989</v>
+      </c>
+      <c r="D157" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="E157" t="n">
+        <v>276.0228</v>
+      </c>
+      <c r="F157" t="n">
+        <v>326.9021</v>
+      </c>
+      <c r="G157" t="n">
+        <v>7.73</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Indian: Maruti Suzuki</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>2y</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>495</v>
+      </c>
+      <c r="D158" t="n">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="E158" t="n">
+        <v>452.6516</v>
+      </c>
+      <c r="F158" t="n">
+        <v>568.2941</v>
+      </c>
+      <c r="G158" t="n">
+        <v>3.12</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Indian: Maruti Suzuki</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>3y</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>741</v>
+      </c>
+      <c r="D159" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="E159" t="n">
+        <v>478.3464</v>
+      </c>
+      <c r="F159" t="n">
+        <v>580.5979</v>
+      </c>
+      <c r="G159" t="n">
+        <v>3.23</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Indian: Maruti Suzuki</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>4y</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>989</v>
+      </c>
+      <c r="D160" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="E160" t="n">
+        <v>2248.6207</v>
+      </c>
+      <c r="F160" t="n">
+        <v>2631.3631</v>
+      </c>
+      <c r="G160" t="n">
+        <v>14.33</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Indian: NTPC Limited</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>2y</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>495</v>
+      </c>
+      <c r="D161" t="n">
+        <v>19.16</v>
+      </c>
+      <c r="E161" t="n">
+        <v>5.6229</v>
+      </c>
+      <c r="F161" t="n">
+        <v>7.3173</v>
+      </c>
+      <c r="G161" t="n">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Indian: NTPC Limited</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>3y</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>741</v>
+      </c>
+      <c r="D162" t="n">
+        <v>19.13</v>
+      </c>
+      <c r="E162" t="n">
+        <v>4.1298</v>
+      </c>
+      <c r="F162" t="n">
+        <v>5.6384</v>
+      </c>
+      <c r="G162" t="n">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Indian: NTPC Limited</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>4y</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>989</v>
+      </c>
+      <c r="D163" t="n">
+        <v>19.19</v>
+      </c>
+      <c r="E163" t="n">
+        <v>3.7659</v>
+      </c>
+      <c r="F163" t="n">
+        <v>5.1062</v>
+      </c>
+      <c r="G163" t="n">
+        <v>1.07</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Indian: Nestlé India</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>2y</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>495</v>
+      </c>
+      <c r="D164" t="n">
+        <v>28.75</v>
+      </c>
+      <c r="E164" t="n">
+        <v>33.1578</v>
+      </c>
+      <c r="F164" t="n">
+        <v>54.7839</v>
+      </c>
+      <c r="G164" t="n">
+        <v>2.41</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Indian: Nestlé India</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>3y</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>741</v>
+      </c>
+      <c r="D165" t="n">
+        <v>28.79</v>
+      </c>
+      <c r="E165" t="n">
+        <v>26.5748</v>
+      </c>
+      <c r="F165" t="n">
+        <v>45.8644</v>
+      </c>
+      <c r="G165" t="n">
+        <v>1.97</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Indian: Nestlé India</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>4y</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>989</v>
+      </c>
+      <c r="D166" t="n">
+        <v>28.76</v>
+      </c>
+      <c r="E166" t="n">
+        <v>23.2361</v>
+      </c>
+      <c r="F166" t="n">
+        <v>40.587</v>
+      </c>
+      <c r="G166" t="n">
+        <v>1.77</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Indian: Power Grid</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>2y</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>495</v>
+      </c>
+      <c r="D167" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="E167" t="n">
+        <v>3.845</v>
+      </c>
+      <c r="F167" t="n">
+        <v>5.5365</v>
+      </c>
+      <c r="G167" t="n">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Indian: Power Grid</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>3y</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>741</v>
+      </c>
+      <c r="D168" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="E168" t="n">
+        <v>3.2416</v>
+      </c>
+      <c r="F168" t="n">
+        <v>4.6936</v>
+      </c>
+      <c r="G168" t="n">
+        <v>1.14</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Indian: Power Grid</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>4y</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>989</v>
+      </c>
+      <c r="D169" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="E169" t="n">
+        <v>3.2891</v>
+      </c>
+      <c r="F169" t="n">
+        <v>4.5576</v>
+      </c>
+      <c r="G169" t="n">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Indian: Reliance Industries</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>2y</t>
+        </is>
+      </c>
+      <c r="C170" t="n">
+        <v>495</v>
+      </c>
+      <c r="D170" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="E170" t="n">
+        <v>19.342</v>
+      </c>
+      <c r="F170" t="n">
+        <v>24.7488</v>
+      </c>
+      <c r="G170" t="n">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Indian: Reliance Industries</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>3y</t>
+        </is>
+      </c>
+      <c r="C171" t="n">
+        <v>741</v>
+      </c>
+      <c r="D171" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="E171" t="n">
+        <v>16.9121</v>
+      </c>
+      <c r="F171" t="n">
+        <v>22.3632</v>
+      </c>
+      <c r="G171" t="n">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Indian: Reliance Industries</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>4y</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>989</v>
+      </c>
+      <c r="D172" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="E172" t="n">
+        <v>16.6024</v>
+      </c>
+      <c r="F172" t="n">
+        <v>21.9428</v>
+      </c>
+      <c r="G172" t="n">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Indian: State Bank of India</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>2y</t>
+        </is>
+      </c>
+      <c r="C173" t="n">
+        <v>495</v>
+      </c>
+      <c r="D173" t="n">
+        <v>28.57</v>
+      </c>
+      <c r="E173" t="n">
+        <v>112.3475</v>
+      </c>
+      <c r="F173" t="n">
+        <v>134.3532</v>
+      </c>
+      <c r="G173" t="n">
+        <v>10.09</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Indian: State Bank of India</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>3y</t>
+        </is>
+      </c>
+      <c r="C174" t="n">
+        <v>741</v>
+      </c>
+      <c r="D174" t="n">
+        <v>28.57</v>
+      </c>
+      <c r="E174" t="n">
+        <v>169.4526</v>
+      </c>
+      <c r="F174" t="n">
+        <v>192.8227</v>
+      </c>
+      <c r="G174" t="n">
+        <v>15.88</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Indian: State Bank of India</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>4y</t>
+        </is>
+      </c>
+      <c r="C175" t="n">
+        <v>989</v>
+      </c>
+      <c r="D175" t="n">
+        <v>28.55</v>
+      </c>
+      <c r="E175" t="n">
+        <v>133.7996</v>
+      </c>
+      <c r="F175" t="n">
+        <v>171.3219</v>
+      </c>
+      <c r="G175" t="n">
+        <v>12.62</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Indian: Sun Pharmaceutical</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>2y</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
+        <v>495</v>
+      </c>
+      <c r="D176" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="E176" t="n">
+        <v>20.728</v>
+      </c>
+      <c r="F176" t="n">
+        <v>27.8092</v>
+      </c>
+      <c r="G176" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Indian: Sun Pharmaceutical</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>3y</t>
+        </is>
+      </c>
+      <c r="C177" t="n">
+        <v>741</v>
+      </c>
+      <c r="D177" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="E177" t="n">
+        <v>18.3747</v>
+      </c>
+      <c r="F177" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="G177" t="n">
+        <v>1.06</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Indian: Sun Pharmaceutical</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>4y</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>989</v>
+      </c>
+      <c r="D178" t="n">
+        <v>6.24</v>
+      </c>
+      <c r="E178" t="n">
+        <v>17.7758</v>
+      </c>
+      <c r="F178" t="n">
+        <v>24.4047</v>
+      </c>
+      <c r="G178" t="n">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Indian: TVS Motor</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>2y</t>
+        </is>
+      </c>
+      <c r="C179" t="n">
+        <v>495</v>
+      </c>
+      <c r="D179" t="n">
+        <v>31.77</v>
+      </c>
+      <c r="E179" t="n">
+        <v>116.105</v>
+      </c>
+      <c r="F179" t="n">
+        <v>143.8244</v>
+      </c>
+      <c r="G179" t="n">
+        <v>3.11</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Indian: TVS Motor</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>3y</t>
+        </is>
+      </c>
+      <c r="C180" t="n">
+        <v>741</v>
+      </c>
+      <c r="D180" t="n">
+        <v>31.77</v>
+      </c>
+      <c r="E180" t="n">
+        <v>153.2816</v>
+      </c>
+      <c r="F180" t="n">
+        <v>193.7652</v>
+      </c>
+      <c r="G180" t="n">
+        <v>4.13</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Indian: TVS Motor</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>4y</t>
+        </is>
+      </c>
+      <c r="C181" t="n">
+        <v>989</v>
+      </c>
+      <c r="D181" t="n">
+        <v>31.82</v>
+      </c>
+      <c r="E181" t="n">
+        <v>665.2839</v>
+      </c>
+      <c r="F181" t="n">
+        <v>704.9729</v>
+      </c>
+      <c r="G181" t="n">
+        <v>18.49</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Indian: Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>2y</t>
+        </is>
+      </c>
+      <c r="C182" t="n">
+        <v>495</v>
+      </c>
+      <c r="D182" t="n">
+        <v>-27.58</v>
+      </c>
+      <c r="E182" t="n">
+        <v>264.1131</v>
+      </c>
+      <c r="F182" t="n">
+        <v>332.2425</v>
+      </c>
+      <c r="G182" t="n">
+        <v>10.49</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Indian: Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>3y</t>
+        </is>
+      </c>
+      <c r="C183" t="n">
+        <v>741</v>
+      </c>
+      <c r="D183" t="n">
+        <v>-27.58</v>
+      </c>
+      <c r="E183" t="n">
+        <v>179.1686</v>
+      </c>
+      <c r="F183" t="n">
+        <v>267.0159</v>
+      </c>
+      <c r="G183" t="n">
+        <v>7.07</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Indian: Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>4y</t>
+        </is>
+      </c>
+      <c r="C184" t="n">
+        <v>989</v>
+      </c>
+      <c r="D184" t="n">
+        <v>-27.58</v>
+      </c>
+      <c r="E184" t="n">
+        <v>89.5399</v>
+      </c>
+      <c r="F184" t="n">
+        <v>137.6693</v>
+      </c>
+      <c r="G184" t="n">
+        <v>3.45</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Indian: Tata Steel</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>2y</t>
+        </is>
+      </c>
+      <c r="C185" t="n">
+        <v>495</v>
+      </c>
+      <c r="D185" t="n">
+        <v>49.45</v>
+      </c>
+      <c r="E185" t="n">
+        <v>16.9587</v>
+      </c>
+      <c r="F185" t="n">
+        <v>20.6039</v>
+      </c>
+      <c r="G185" t="n">
+        <v>8.279999999999999</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Indian: Tata Steel</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>3y</t>
+        </is>
+      </c>
+      <c r="C186" t="n">
+        <v>741</v>
+      </c>
+      <c r="D186" t="n">
+        <v>49.45</v>
+      </c>
+      <c r="E186" t="n">
+        <v>17.7565</v>
+      </c>
+      <c r="F186" t="n">
+        <v>22.8822</v>
+      </c>
+      <c r="G186" t="n">
+        <v>8.85</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Indian: Tata Steel</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>4y</t>
+        </is>
+      </c>
+      <c r="C187" t="n">
+        <v>989</v>
+      </c>
+      <c r="D187" t="n">
+        <v>49.47</v>
+      </c>
+      <c r="E187" t="n">
+        <v>13.6419</v>
+      </c>
+      <c r="F187" t="n">
+        <v>19.6148</v>
+      </c>
+      <c r="G187" t="n">
+        <v>6.86</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Indian: Titan Company</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>2y</t>
+        </is>
+      </c>
+      <c r="C188" t="n">
+        <v>495</v>
+      </c>
+      <c r="D188" t="n">
+        <v>27.04</v>
+      </c>
+      <c r="E188" t="n">
+        <v>355.5057</v>
+      </c>
+      <c r="F188" t="n">
+        <v>398.086</v>
+      </c>
+      <c r="G188" t="n">
+        <v>8.32</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Indian: Titan Company</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>3y</t>
+        </is>
+      </c>
+      <c r="C189" t="n">
+        <v>741</v>
+      </c>
+      <c r="D189" t="n">
+        <v>27.05</v>
+      </c>
+      <c r="E189" t="n">
+        <v>350.1347</v>
+      </c>
+      <c r="F189" t="n">
+        <v>426.0753</v>
+      </c>
+      <c r="G189" t="n">
+        <v>8.31</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Indian: Titan Company</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>4y</t>
+        </is>
+      </c>
+      <c r="C190" t="n">
+        <v>989</v>
+      </c>
+      <c r="D190" t="n">
+        <v>27.05</v>
+      </c>
+      <c r="E190" t="n">
+        <v>268.9401</v>
+      </c>
+      <c r="F190" t="n">
+        <v>367.2117</v>
+      </c>
+      <c r="G190" t="n">
+        <v>6.42</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Indian: UltraTech Cement</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>2y</t>
+        </is>
+      </c>
+      <c r="C191" t="n">
+        <v>495</v>
+      </c>
+      <c r="D191" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="E191" t="n">
+        <v>205.7323</v>
+      </c>
+      <c r="F191" t="n">
+        <v>257.6248</v>
+      </c>
+      <c r="G191" t="n">
+        <v>1.74</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Indian: UltraTech Cement</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>3y</t>
+        </is>
+      </c>
+      <c r="C192" t="n">
+        <v>741</v>
+      </c>
+      <c r="D192" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E192" t="n">
+        <v>168.6566</v>
+      </c>
+      <c r="F192" t="n">
+        <v>219.5721</v>
+      </c>
+      <c r="G192" t="n">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Indian: UltraTech Cement</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>4y</t>
+        </is>
+      </c>
+      <c r="C193" t="n">
+        <v>989</v>
+      </c>
+      <c r="D193" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="E193" t="n">
+        <v>214.0876</v>
+      </c>
+      <c r="F193" t="n">
+        <v>279.7575</v>
+      </c>
+      <c r="G193" t="n">
+        <v>1.76</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
           <t>Indian: Wipro</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>4y</t>
-        </is>
-      </c>
-      <c r="C121" t="n">
-        <v>987</v>
-      </c>
-      <c r="D121" t="n">
-        <v>-13.8</v>
-      </c>
-      <c r="E121" t="n">
-        <v>2.8449</v>
-      </c>
-      <c r="F121" t="n">
-        <v>4.0253</v>
-      </c>
-      <c r="G121" t="n">
-        <v>1.23</v>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>2y</t>
+        </is>
+      </c>
+      <c r="C194" t="n">
+        <v>495</v>
+      </c>
+      <c r="D194" t="n">
+        <v>-15.33</v>
+      </c>
+      <c r="E194" t="n">
+        <v>12.2278</v>
+      </c>
+      <c r="F194" t="n">
+        <v>15.21</v>
+      </c>
+      <c r="G194" t="n">
+        <v>6.03</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Indian: Wipro</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>3y</t>
+        </is>
+      </c>
+      <c r="C195" t="n">
+        <v>741</v>
+      </c>
+      <c r="D195" t="n">
+        <v>-15.33</v>
+      </c>
+      <c r="E195" t="n">
+        <v>3.0401</v>
+      </c>
+      <c r="F195" t="n">
+        <v>4.2654</v>
+      </c>
+      <c r="G195" t="n">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Indian: Wipro</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>4y</t>
+        </is>
+      </c>
+      <c r="C196" t="n">
+        <v>989</v>
+      </c>
+      <c r="D196" t="n">
+        <v>-15.34</v>
+      </c>
+      <c r="E196" t="n">
+        <v>2.7782</v>
+      </c>
+      <c r="F196" t="n">
+        <v>3.9582</v>
+      </c>
+      <c r="G196" t="n">
+        <v>1.22</v>
       </c>
     </row>
   </sheetData>
